--- a/StructureDefinition-openimis-invoice-invoice.xlsx
+++ b/StructureDefinition-openimis-invoice-invoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10146,7 +10146,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -10828,7 +10828,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -11394,7 +11394,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>22</v>
@@ -12186,7 +12186,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>22</v>
@@ -12754,7 +12754,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>22</v>
@@ -15698,7 +15698,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-invoice-invoice.xlsx
+++ b/StructureDefinition-openimis-invoice-invoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-invoice-invoice.xlsx
+++ b/StructureDefinition-openimis-invoice-invoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
